--- a/results/andar_할인율모니터링_20260915.xlsx
+++ b/results/andar_할인율모니터링_20260915.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3,570</t>
+          <t>3,571</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3,570</t>
+          <t>3,571</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1087,153 +1087,153 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EPTBG-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>서밋 유틸리티 백팩</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTBG-11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>안다르 실버 리유저블백 L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EJFMT-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>10,099</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EPTBG-11</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 L</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1255,121 +1255,121 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EJFMT-01</t>
+          <t>EPTBG-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
+          <t>에어플라이 프리런 러닝 벨트</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10,097</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EPTBG-02</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>서밋 유틸리티 백팩</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EOTBG-13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>멀티 포켓 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1381,37 +1381,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EOTBG-13</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>멀티 포켓 숄더 앤 크로스백</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1423,79 +1423,79 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1507,84 +1507,84 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPTBG-01</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>에어플라이 프리런 러닝 벨트</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1,411</t>
+          <t>1,412</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1801,121 +1801,121 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ENTBG-05</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>미니 숄더 앤 크로스백</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5,140</t>
+          <t>2,019</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>692</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>ENTBG-05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>미니 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>5,140</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1927,37 +1927,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EOTBG-15</t>
+          <t>ENTSO-02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>폴더블 짐백 2.0</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1,042</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENTSO-02</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2011,37 +2011,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1,042</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2053,37 +2053,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>3,211</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2095,37 +2095,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>3,211</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2137,37 +2137,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>EOTBG-15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>폴더블 짐백 2.0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2179,37 +2179,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3,211</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2221,42 +2221,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3,211</t>
+          <t>3,027</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2305,37 +2305,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>안다르 실버 리유저블백 M</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3,027</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2389,69 +2389,69 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 M</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2461,29 +2461,29 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13843&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ENTBG-16</t>
+          <t>EOTBG-02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>라이트 패딩 쇼퍼백</t>
+          <t>액티브 라이트 백팩</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>382</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2557,27 +2557,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2587,54 +2587,54 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>735</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13843&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EOTBG-02</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>액티브 라이트 백팩</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>819</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2683,59 +2683,59 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>ENTBG-16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>라이트 패딩 쇼퍼백</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2755,49 +2755,49 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>624</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1,109</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2809,27 +2809,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6,594</t>
+          <t>1,110</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2851,27 +2851,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EOTCP-05</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2881,39 +2881,39 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>6,595</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EJPFR-04</t>
+          <t>EOTCP-05</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>릴렉스 폼롤러 Ⅱ</t>
+          <t>히트 런 이어플랩 캡</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>6,367</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2977,42 +2977,42 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EJPFR-04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>릴렉스 폼롤러 Ⅱ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>6,367</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3187,27 +3187,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -3271,37 +3271,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3313,59 +3313,59 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3375,49 +3375,49 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3427,39 +3427,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3469,49 +3469,49 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>846</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3523,27 +3523,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3553,39 +3553,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>636</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>테이핑 러닝 삭스</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3595,54 +3595,54 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -3775,27 +3775,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3805,39 +3805,39 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3847,71 +3847,71 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1,538</t>
+          <t>586</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3931,39 +3931,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3985,27 +3985,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4015,39 +4015,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>2,116</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4057,39 +4057,39 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2,116</t>
+          <t>568</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4153,27 +4153,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4183,39 +4183,39 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EPTCP-02</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>시그니처 로고 나일론 볼캡</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4225,39 +4225,39 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>772</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4279,37 +4279,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4321,121 +4321,121 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4447,37 +4447,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4489,37 +4489,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4531,27 +4531,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EPTCP-02</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>시그니처 로고 나일론 볼캡</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4561,39 +4561,39 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4603,39 +4603,39 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4645,81 +4645,81 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1,330</t>
+          <t>723</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4729,39 +4729,39 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1,330</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1,093</t>
+          <t>479</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4783,27 +4783,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>EKPMB-02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>릴렉스 미니 짐볼</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4813,39 +4813,39 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>1,232</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EKPMB-02</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>릴렉스 미니 짐볼</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4855,39 +4855,39 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1,230</t>
+          <t>1,093</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4897,39 +4897,39 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4939,49 +4939,49 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 발목 보호대</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>697</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4993,27 +4993,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EMTBG-03</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>숄더 앤 크로스백</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5023,39 +5023,39 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>8,135</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5065,49 +5065,49 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>753</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EMTBG-03</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8,136</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5119,163 +5119,163 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>[1&amp;1] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>723</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ENTET-02</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 2kg</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>필라테스 앵클 삭스</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5287,27 +5287,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ENTMU-01</t>
+          <t>ENTET-02</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>소프트 니트 머플러</t>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5317,81 +5317,81 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>ENTMU-01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>소프트 니트 머플러</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5413,27 +5413,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EOTBG-04</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>데님 포켓 숄더백</t>
+          <t>필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5443,39 +5443,39 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5485,39 +5485,39 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>696</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5527,123 +5527,123 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>527</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5653,81 +5653,81 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>4,136</t>
+          <t>1,538</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EOTET-01</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>소프트 뱀부 롱 타월</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EMTRB-01</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1,375</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5749,27 +5749,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EMTRB-02</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1,375</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5791,27 +5791,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EMTRB-03</t>
+          <t>EOTET-01</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>소프트 뱀부 롱 타월</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1,375</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5833,27 +5833,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EOTSC-11</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>웜 레그 롱 워머</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5875,27 +5875,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>EOTBG-04</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>데님 포켓 숄더백</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5917,27 +5917,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EOTSC-11</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>웜 레그 롱 워머</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5947,34 +5947,34 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>913</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6001,17 +6001,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6021,49 +6021,49 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EMTRB-01</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6073,39 +6073,39 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>1,375</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>EMTRB-02</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6115,39 +6115,39 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1,375</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>EMTRB-03</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>1,375</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6169,27 +6169,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EOTMU-01</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>스트링 패딩 넥워머</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6199,49 +6199,49 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6253,37 +6253,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>4,136</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6295,91 +6295,91 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6389,27 +6389,27 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6421,111 +6421,111 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EOTMU-01</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>스트링 패딩 넥워머</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6535,39 +6535,39 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6577,29 +6577,29 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6619,91 +6619,91 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>31,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>26,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6715,27 +6715,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6745,12 +6745,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>2,019</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -6799,27 +6799,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6829,39 +6829,39 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6871,39 +6871,39 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6913,39 +6913,39 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>ENTCP-05</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>소프트 니트 비니</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6967,69 +6967,69 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ENTCP-05</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>소프트 니트 비니</t>
+          <t>하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7039,49 +7039,49 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7093,27 +7093,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>ENTCP-01</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>하이 서포트 팔꿈치 보호대</t>
+          <t>와이드 셰이드 버킷햇</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7123,39 +7123,39 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>686</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ENTCP-01</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>와이드 셰이드 버킷햇</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7165,39 +7165,39 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>EOTBG-05</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>메쉬 포켓 비치백</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7219,27 +7219,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EOTBG-05</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>메쉬 포켓 비치백</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7345,111 +7345,111 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>ENTGL-05</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>니트 글러브</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ENTGL-05</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>니트 글러브</t>
+          <t>맨즈 논슬립 하프 토삭스</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7765,27 +7765,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 하프 토삭스</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7795,52 +7795,10 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>EKPET-01</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>20,900</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>20,900</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
